--- a/jogos_2024-10-09.xlsx
+++ b/jogos_2024-10-09.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
         <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.82</v>
+        <v>2.38</v>
       </c>
       <c r="M6" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>4.89</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="S6" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="X6" t="n">
-        <v>3.65</v>
+        <v>2.24</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.65</v>
+        <v>2.63</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['19', '81']</t>
+          <t>['19', '81', '90+7']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2', '45+1']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45574.83333333334</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.38</v>
+        <v>1.82</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>4.89</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="T7" t="n">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="U7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.25</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.62</v>
-      </c>
       <c r="X7" t="n">
-        <v>2.24</v>
+        <v>3.65</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.29</v>
+        <v>1.91</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.63</v>
+        <v>1.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['19', '81', '90+7']</t>
+          <t>['19', '81']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['2', '45+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45574.83333333334</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,28 +1572,28 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="M9" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="N9" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T9" t="n">
         <v>2.75</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>['83', '88']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['45+3', '59']</t>
+          <t>['53', '63']</t>
         </is>
       </c>
       <c r="AG9" t="n">
@@ -1645,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45574.91666666666</v>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,28 +1701,28 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="M10" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="N10" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.75</v>
       </c>
       <c r="T10" t="n">
         <v>2.75</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['83', '88']</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['53', '63']</t>
+          <t>['45+3', '59']</t>
         </is>
       </c>
       <c r="AG10" t="n">
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45574.91666666666</v>
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.33</v>
+        <v>1.47</v>
       </c>
       <c r="M11" t="n">
-        <v>2.42</v>
+        <v>4.21</v>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>6.44</v>
       </c>
       <c r="O11" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="R11" t="n">
         <v>1.36</v>
       </c>
       <c r="S11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA11" t="n">
         <v>3</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.97</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['32', '90+5']</t>
+          <t>['15', '78']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '90+3']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.85</v>
+        <v>1.48</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45574.95833333334</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.47</v>
+        <v>3.33</v>
       </c>
       <c r="M12" t="n">
-        <v>4.21</v>
+        <v>2.42</v>
       </c>
       <c r="N12" t="n">
-        <v>6.44</v>
+        <v>2.54</v>
       </c>
       <c r="O12" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
         <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X12" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['15', '78']</t>
+          <t>['32', '90+5']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['21', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45574.95833333334</v>
